--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CAJA RURAL CB ZAMORA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CAJA RURAL CB ZAMORA.xlsx
@@ -565,13 +565,13 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>78.2572</v>
+        <v>64.9764</v>
       </c>
       <c r="E2" t="n">
-        <v>66.08450000000001</v>
+        <v>54.7502</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1728</v>
+        <v>10.2264</v>
       </c>
       <c r="G2" t="n">
         <v>-1.1435</v>
@@ -610,13 +610,13 @@
         <v>46.9812</v>
       </c>
       <c r="S2" t="n">
-        <v>26.2757</v>
+        <v>12.9946</v>
       </c>
       <c r="T2" t="n">
-        <v>20.3126</v>
+        <v>8.978200000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>5.9626</v>
+        <v>4.0163</v>
       </c>
       <c r="V2" t="n">
         <v>37.4644</v>
@@ -643,13 +643,13 @@
         <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>10.4269</v>
+        <v>21.2441</v>
       </c>
       <c r="E3" t="n">
-        <v>9.316500000000001</v>
+        <v>15.5099</v>
       </c>
       <c r="F3" t="n">
-        <v>1.11</v>
+        <v>5.7341</v>
       </c>
       <c r="G3" t="n">
         <v>17.7053</v>
@@ -688,13 +688,13 @@
         <v>38.4983</v>
       </c>
       <c r="S3" t="n">
-        <v>-15.4418</v>
+        <v>-4.624</v>
       </c>
       <c r="T3" t="n">
-        <v>-7.6089</v>
+        <v>-1.4152</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.8325</v>
+        <v>-3.2087</v>
       </c>
       <c r="V3" t="n">
         <v>-9.672499999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>7.743399999999999</v>
+        <v>5.460800000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>15.1607</v>
+        <v>22.2976</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.4175</v>
+        <v>-16.8369</v>
       </c>
       <c r="G4" t="n">
-        <v>-24.0205</v>
+        <v>-1.996799999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-14.2313</v>
+        <v>9.689299999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-9.789099999999999</v>
+        <v>-11.6862</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2018</v>
+        <v>34.058</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7707000000000003</v>
+        <v>24.7973</v>
       </c>
       <c r="L4" t="n">
-        <v>4.9716</v>
+        <v>9.2607</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.222</v>
+        <v>-36.0548</v>
       </c>
       <c r="N4" t="n">
-        <v>-13.4608</v>
+        <v>-15.108</v>
       </c>
       <c r="O4" t="n">
-        <v>-14.7614</v>
+        <v>-20.9471</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4353000000000007</v>
+        <v>-21.533</v>
       </c>
       <c r="Q4" t="n">
-        <v>-35.2357</v>
+        <v>-61.772</v>
       </c>
       <c r="R4" t="n">
-        <v>34.8007</v>
+        <v>40.238</v>
       </c>
       <c r="S4" t="n">
-        <v>30.0008</v>
+        <v>-4.8883</v>
       </c>
       <c r="T4" t="n">
-        <v>21.0168</v>
+        <v>-3.0256</v>
       </c>
       <c r="U4" t="n">
-        <v>8.983599999999999</v>
+        <v>-1.8624</v>
       </c>
       <c r="V4" t="n">
-        <v>2.198499999999999</v>
+        <v>33.8791</v>
       </c>
       <c r="W4" t="n">
-        <v>25.1786</v>
+        <v>53.0379</v>
       </c>
       <c r="X4" t="n">
-        <v>-22.9806</v>
+        <v>-19.1587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.271399999999999</v>
+        <v>0.6448000000000003</v>
       </c>
       <c r="E5" t="n">
-        <v>17.8389</v>
+        <v>-0.3668000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-11.5672</v>
+        <v>1.0114</v>
       </c>
       <c r="G5" t="n">
-        <v>3.097700000000001</v>
+        <v>-0.3611000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>8.978299999999999</v>
+        <v>-1.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.8809</v>
+        <v>0.7187000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>27.8468</v>
+        <v>0.3003999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>22.224</v>
+        <v>-0.5626</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6222</v>
+        <v>0.8630000000000002</v>
       </c>
       <c r="M5" t="n">
-        <v>-24.7496</v>
+        <v>-0.6616</v>
       </c>
       <c r="N5" t="n">
-        <v>-13.2463</v>
+        <v>-0.5173</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.5038</v>
+        <v>-0.1443</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3054</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>-37.8458</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>36.541</v>
+        <v>1.74</v>
       </c>
       <c r="S5" t="n">
-        <v>23.7393</v>
+        <v>-0.5597</v>
       </c>
       <c r="T5" t="n">
-        <v>22.5464</v>
+        <v>-0.4927</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1928</v>
+        <v>-0.067</v>
       </c>
       <c r="V5" t="n">
-        <v>-19.2606</v>
+        <v>-0.1745</v>
       </c>
       <c r="W5" t="n">
-        <v>5.2917</v>
+        <v>-0.1745</v>
       </c>
       <c r="X5" t="n">
-        <v>-24.5525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>C. ARRANZ BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,67 +874,67 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1726000000000001</v>
+        <v>-0.7957</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5469999999999998</v>
+        <v>-0.8136</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3744</v>
+        <v>0.0179</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3611000000000001</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0799</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7187000000000001</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3003999999999999</v>
+        <v>-0.7451</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5626</v>
+        <v>-0.7451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8630000000000002</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6616</v>
+        <v>0.1155</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5173</v>
+        <v>0.1155</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1443</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.377</v>
+        <v>-0.1661</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.673</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7041000000000001</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. PREPELIC</t>
+          <t>P. MONTESDEOCA SANTANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8429999999999995</v>
+        <v>-1.1597</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.028600000000001</v>
+        <v>-1.3601</v>
       </c>
       <c r="F7" t="n">
-        <v>5.1855</v>
+        <v>0.2004</v>
       </c>
       <c r="G7" t="n">
-        <v>-11.922</v>
+        <v>-1.0248</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.885</v>
+        <v>0.3163</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.0371</v>
+        <v>-1.3411</v>
       </c>
       <c r="J7" t="n">
-        <v>-6.7474</v>
+        <v>-1.4719</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.129</v>
+        <v>0.0182</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6185</v>
+        <v>-1.4901</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.1749</v>
+        <v>0.447</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7562</v>
+        <v>0.298</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.4186</v>
+        <v>0.149</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.9177</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>10.6577</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>8.404300000000001</v>
+        <v>-0.1349</v>
       </c>
       <c r="T7" t="n">
-        <v>6.4005</v>
+        <v>0.1118</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0039</v>
+        <v>-0.2466</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.236</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ARRANZ BLANCO</t>
+          <t>R. HERNANDEZ GALLARDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,40 +1030,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.895</v>
+        <v>-1.4325</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.882</v>
+        <v>0.04410000000000003</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0129</v>
+        <v>-1.4767</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6294999999999999</v>
+        <v>0.3772</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6294999999999999</v>
+        <v>0.3772</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7451</v>
+        <v>0.1126</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7451</v>
+        <v>0.1126</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1155</v>
+        <v>0.2645</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1155</v>
+        <v>0.2645</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1078,28 +1078,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2655</v>
+        <v>-0.1147</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.137</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1285</v>
+        <v>-0.0462</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MONTESDEOCA SANTANA</t>
+          <t>B. PREPELIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3023</v>
+        <v>-4.201700000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4719</v>
+        <v>-9.125499999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1696</v>
+        <v>4.9238</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0248</v>
+        <v>-11.922</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3163</v>
+        <v>-6.885</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3411</v>
+        <v>-5.0371</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4719</v>
+        <v>-6.7474</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0182</v>
+        <v>-5.129</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4901</v>
+        <v>-1.6185</v>
       </c>
       <c r="M9" t="n">
-        <v>0.447</v>
+        <v>-5.1749</v>
       </c>
       <c r="N9" t="n">
-        <v>0.298</v>
+        <v>-1.7562</v>
       </c>
       <c r="O9" t="n">
-        <v>0.149</v>
+        <v>-3.4186</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-8.9177</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>10.6577</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2775</v>
+        <v>5.0456</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.3035</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2775</v>
+        <v>1.7419</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.236</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.3013</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. HERNANDEZ GALLARDO</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5626</v>
+        <v>-4.787700000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02429999999999999</v>
+        <v>3.609699999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5383</v>
+        <v>-8.396899999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3772</v>
+        <v>-4.479799999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3772</v>
+        <v>-8.625499999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4.1457</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1126</v>
+        <v>20.6309</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1126</v>
+        <v>3.6159</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>17.0151</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2645</v>
+        <v>-25.1106</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2645</v>
+        <v>-12.2415</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-12.8692</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-21.3154</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-58.2919</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>36.9762</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.245</v>
+        <v>-0.3385</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.137</v>
+        <v>0.8990999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.108</v>
+        <v>-1.2377</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.695</v>
+        <v>21.3464</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>40.3713</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.695</v>
+        <v>-19.0251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.3585</v>
+        <v>-7.5114</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.232899999999999</v>
+        <v>4.1071</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1251</v>
+        <v>-11.6184</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.3464</v>
+        <v>3.097700000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.301500000000001</v>
+        <v>8.978299999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-9.0451</v>
+        <v>-5.8809</v>
       </c>
       <c r="J11" t="n">
-        <v>22.3814</v>
+        <v>27.8468</v>
       </c>
       <c r="K11" t="n">
-        <v>14.7072</v>
+        <v>22.224</v>
       </c>
       <c r="L11" t="n">
-        <v>7.674</v>
+        <v>5.6222</v>
       </c>
       <c r="M11" t="n">
-        <v>-36.7279</v>
+        <v>-24.7496</v>
       </c>
       <c r="N11" t="n">
-        <v>-20.0083</v>
+        <v>-13.2463</v>
       </c>
       <c r="O11" t="n">
-        <v>-16.7195</v>
+        <v>-11.5038</v>
       </c>
       <c r="P11" t="n">
-        <v>-9.135200000000001</v>
+        <v>-1.3054</v>
       </c>
       <c r="Q11" t="n">
-        <v>-53.0717</v>
+        <v>-37.8458</v>
       </c>
       <c r="R11" t="n">
-        <v>43.936</v>
+        <v>36.541</v>
       </c>
       <c r="S11" t="n">
-        <v>6.7179</v>
+        <v>9.956300000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>6.217700000000001</v>
+        <v>8.8148</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5001</v>
+        <v>1.1418</v>
       </c>
       <c r="V11" t="n">
-        <v>6.4051</v>
+        <v>-19.2606</v>
       </c>
       <c r="W11" t="n">
-        <v>17.2393</v>
+        <v>5.2917</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.8341</v>
+        <v>-24.5525</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.7131</v>
+        <v>-10.209</v>
       </c>
       <c r="E12" t="n">
-        <v>8.057999999999998</v>
+        <v>0.0198999999999987</v>
       </c>
       <c r="F12" t="n">
-        <v>-19.7708</v>
+        <v>-10.2288</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.996799999999999</v>
+        <v>-2.7802</v>
       </c>
       <c r="H12" t="n">
-        <v>9.689299999999999</v>
+        <v>5.299099999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.6862</v>
+        <v>-8.079800000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>34.058</v>
+        <v>10.2409</v>
       </c>
       <c r="K12" t="n">
-        <v>24.7973</v>
+        <v>8.745900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>9.2607</v>
+        <v>1.4945</v>
       </c>
       <c r="M12" t="n">
-        <v>-36.0548</v>
+        <v>-13.0215</v>
       </c>
       <c r="N12" t="n">
-        <v>-15.108</v>
+        <v>-3.4469</v>
       </c>
       <c r="O12" t="n">
-        <v>-20.9471</v>
+        <v>-9.5747</v>
       </c>
       <c r="P12" t="n">
-        <v>-21.533</v>
+        <v>9.3527</v>
       </c>
       <c r="Q12" t="n">
-        <v>-61.772</v>
+        <v>-14.1377</v>
       </c>
       <c r="R12" t="n">
-        <v>40.238</v>
+        <v>23.4903</v>
       </c>
       <c r="S12" t="n">
-        <v>-22.0621</v>
+        <v>-2.5779</v>
       </c>
       <c r="T12" t="n">
-        <v>-17.2656</v>
+        <v>-0.8602000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.7959</v>
+        <v>-1.7176</v>
       </c>
       <c r="V12" t="n">
-        <v>33.8791</v>
+        <v>-14.2033</v>
       </c>
       <c r="W12" t="n">
-        <v>53.0379</v>
+        <v>4.7772</v>
       </c>
       <c r="X12" t="n">
-        <v>-19.1587</v>
+        <v>-18.9805</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.4703</v>
+        <v>-10.7635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8563999999999996</v>
+        <v>0.7226999999999992</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.3272</v>
+        <v>-11.4856</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7802</v>
+        <v>-24.0205</v>
       </c>
       <c r="H13" t="n">
-        <v>5.299099999999999</v>
+        <v>-14.2313</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.079800000000001</v>
+        <v>-9.789099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>10.2409</v>
+        <v>4.2018</v>
       </c>
       <c r="K13" t="n">
-        <v>8.745900000000001</v>
+        <v>-0.7707000000000003</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4945</v>
+        <v>4.9716</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.0215</v>
+        <v>-28.222</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.4469</v>
+        <v>-13.4608</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.5747</v>
+        <v>-14.7614</v>
       </c>
       <c r="P13" t="n">
-        <v>9.3527</v>
+        <v>-0.4353000000000007</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.1377</v>
+        <v>-35.2357</v>
       </c>
       <c r="R13" t="n">
-        <v>23.4903</v>
+        <v>34.8007</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8396</v>
+        <v>11.4942</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.02410000000000001</v>
+        <v>6.5784</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.8158</v>
+        <v>4.9156</v>
       </c>
       <c r="V13" t="n">
-        <v>-14.2033</v>
+        <v>2.198499999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>4.7772</v>
+        <v>25.1786</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.9805</v>
+        <v>-22.9806</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.9939</v>
+        <v>-14.0352</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.562</v>
+        <v>-9.4719</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.4318</v>
+        <v>-4.563599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.479799999999999</v>
+        <v>-14.3464</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.625499999999999</v>
+        <v>-5.301500000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1457</v>
+        <v>-9.0451</v>
       </c>
       <c r="J14" t="n">
-        <v>20.6309</v>
+        <v>22.3814</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6159</v>
+        <v>14.7072</v>
       </c>
       <c r="L14" t="n">
-        <v>17.0151</v>
+        <v>7.674</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.1106</v>
+        <v>-36.7279</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.2415</v>
+        <v>-20.0083</v>
       </c>
       <c r="O14" t="n">
-        <v>-12.8692</v>
+        <v>-16.7195</v>
       </c>
       <c r="P14" t="n">
-        <v>-21.3154</v>
+        <v>-9.135200000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-58.2919</v>
+        <v>-53.0717</v>
       </c>
       <c r="R14" t="n">
-        <v>36.9762</v>
+        <v>43.936</v>
       </c>
       <c r="S14" t="n">
-        <v>-19.5449</v>
+        <v>3.0413</v>
       </c>
       <c r="T14" t="n">
-        <v>-13.2722</v>
+        <v>3.9792</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.2725</v>
+        <v>-0.9378</v>
       </c>
       <c r="V14" t="n">
-        <v>21.3464</v>
+        <v>6.4051</v>
       </c>
       <c r="W14" t="n">
-        <v>40.3713</v>
+        <v>17.2393</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.0251</v>
+        <v>-10.8341</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>-28.1969</v>
+        <v>-21.1655</v>
       </c>
       <c r="E15" t="n">
-        <v>-25.595</v>
+        <v>-20.3208</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6018</v>
+        <v>-0.8444000000000009</v>
       </c>
       <c r="G15" t="n">
         <v>18.3228</v>
@@ -1624,13 +1624,13 @@
         <v>44.8064</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.6682</v>
+        <v>-0.6364000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.1247</v>
+        <v>-1.8502</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5431000000000001</v>
+        <v>1.2138</v>
       </c>
       <c r="V15" t="n">
         <v>-14.4908</v>
@@ -1657,13 +1657,13 @@
         <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>-30.2672</v>
+        <v>-22.4222</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.9786</v>
+        <v>-9.082800000000002</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.2886</v>
+        <v>-13.3395</v>
       </c>
       <c r="G16" t="n">
         <v>-29.1116</v>
@@ -1702,13 +1702,13 @@
         <v>44.5889</v>
       </c>
       <c r="S16" t="n">
-        <v>-12.2923</v>
+        <v>-4.4474</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.2798</v>
+        <v>-0.3842000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.0125</v>
+        <v>-4.0634</v>
       </c>
       <c r="V16" t="n">
         <v>13.5294</v>
@@ -1735,13 +1735,13 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>-58.059</v>
+        <v>-37.676</v>
       </c>
       <c r="E17" t="n">
-        <v>-33.0469</v>
+        <v>-20.9305</v>
       </c>
       <c r="F17" t="n">
-        <v>-25.0122</v>
+        <v>-16.7458</v>
       </c>
       <c r="G17" t="n">
         <v>-22.7798</v>
@@ -1780,13 +1780,13 @@
         <v>42.6308</v>
       </c>
       <c r="S17" t="n">
-        <v>-25.1967</v>
+        <v>-4.8136</v>
       </c>
       <c r="T17" t="n">
-        <v>-12.5549</v>
+        <v>-0.4383</v>
       </c>
       <c r="U17" t="n">
-        <v>-12.6414</v>
+        <v>-4.3749</v>
       </c>
       <c r="V17" t="n">
         <v>-3.9927</v>
@@ -1813,13 +1813,13 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>-77.13549999999999</v>
+        <v>-43.834</v>
       </c>
       <c r="E18" t="n">
-        <v>17.94580000000001</v>
+        <v>29.58920000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-95.08109999999999</v>
+        <v>-73.4226</v>
       </c>
       <c r="G18" t="n">
         <v>-75.09299999999999</v>
@@ -1849,25 +1849,25 @@
         <v>-154.5069</v>
       </c>
       <c r="P18" t="n">
-        <v>-40.23940000000001</v>
+        <v>-40.2394</v>
       </c>
       <c r="Q18" t="n">
-        <v>-486.1252999999999</v>
+        <v>-486.1253</v>
       </c>
       <c r="R18" t="n">
         <v>445.8855</v>
       </c>
       <c r="S18" t="n">
-        <v>-14.07259999999999</v>
+        <v>19.2305</v>
       </c>
       <c r="T18" t="n">
-        <v>12.41680000000001</v>
+        <v>24.0616</v>
       </c>
       <c r="U18" t="n">
-        <v>-26.4888</v>
+        <v>-4.8305</v>
       </c>
       <c r="V18" t="n">
-        <v>52.26819999999999</v>
+        <v>52.2682</v>
       </c>
       <c r="W18" t="n">
         <v>255.8252</v>
